--- a/data/trans_orig/P6706-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6706-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2012</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2012 (tasa de respuesta: 98,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47815</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74859</t>
+          <t>74924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>47438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78780</t>
+          <t>77908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116349</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>32084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58123</t>
+          <t>57397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83180</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>41552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>68966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48676</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74169</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110200</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>51993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77507</t>
+          <t>77495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>84936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52881</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91261</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129502</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63270</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95644</t>
+          <t>95294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141375</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>58923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>92657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60173</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>92099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36134</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62355</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103006</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>143474</t>
+          <t>144221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67243</t>
+          <t>67019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99959</t>
+          <t>100684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74050</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124467</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169388</t>
+          <t>167397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110282</t>
+          <t>108242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148595</t>
+          <t>150101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66968</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186910</t>
+          <t>187272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238115</t>
+          <t>236996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68646</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102153</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>43349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74161</t>
+          <t>72417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66935</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30953</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77393</t>
+          <t>76051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113667</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56490</t>
+          <t>54532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>86822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83381</t>
+          <t>81640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119885</t>
+          <t>119043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96605</t>
+          <t>98557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133405</t>
+          <t>134912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98003</t>
+          <t>97779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175930</t>
+          <t>177037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223533</t>
+          <t>222082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82337</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57007</t>
+          <t>59110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88180</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127334</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61675</t>
+          <t>60007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>40729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59863</t>
+          <t>60657</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93519</t>
+          <t>93426</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82679</t>
+          <t>81943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118442</t>
+          <t>116887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>57042</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85361</t>
+          <t>85175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>146952</t>
+          <t>148684</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>190872</t>
+          <t>192943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89304</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124853</t>
+          <t>125695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>50379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78762</t>
+          <t>79126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148547</t>
+          <t>148165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193772</t>
+          <t>193102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78909</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>114502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78090</t>
+          <t>78799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109591</t>
+          <t>111305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165814</t>
+          <t>167461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>215632</t>
+          <t>213833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>226725</t>
+          <t>229336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>287514</t>
+          <t>288008</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>132484</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>177230</t>
+          <t>180651</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>373360</t>
+          <t>371716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>449832</t>
+          <t>443911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>138526</t>
+          <t>138138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>188450</t>
+          <t>187647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92314</t>
+          <t>92323</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134358</t>
+          <t>135546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>243925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>304482</t>
+          <t>305534</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>251867</t>
+          <t>249378</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>312419</t>
+          <t>314760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,82 +3701,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>196190</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>170481</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>224921</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>18,15%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>476976</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>437739</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>521130</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>22,21%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>196190</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>171788</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>222559</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>476976</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>438113</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>519234</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>269478</t>
+          <t>268148</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>333263</t>
+          <t>333994</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>153888</t>
+          <t>156088</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>204026</t>
+          <t>206083</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>440861</t>
+          <t>441441</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>517213</t>
+          <t>521942</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>373048</t>
+          <t>373341</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>441680</t>
+          <t>445488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>270626</t>
+          <t>270177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>330073</t>
+          <t>330129</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>659493</t>
+          <t>665191</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>751199</t>
+          <t>760057</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2016</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59023</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>60778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>94339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55762</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>46863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>62801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94147</t>
+          <t>95214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>64033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52428</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74372</t>
+          <t>74618</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108041</t>
+          <t>108362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43635</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69724</t>
+          <t>69579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>71781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105982</t>
+          <t>105555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62969</t>
+          <t>64288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62551</t>
+          <t>62683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94537</t>
+          <t>95080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67132</t>
+          <t>67196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102572</t>
+          <t>100046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104966</t>
+          <t>104951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145031</t>
+          <t>145234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>58553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92195</t>
+          <t>92777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93513</t>
+          <t>93605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132739</t>
+          <t>135212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>61066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94750</t>
+          <t>95035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79870</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120867</t>
+          <t>120575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163530</t>
+          <t>165789</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79131</t>
+          <t>77275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114806</t>
+          <t>113889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>40257</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>65574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125561</t>
+          <t>124900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>167628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>65993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>100366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66203</t>
+          <t>66373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97306</t>
+          <t>95521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>141200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184799</t>
+          <t>185764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58353</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90672</t>
+          <t>93332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41186</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86560</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124875</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69886</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>50850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74704</t>
+          <t>75138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110707</t>
+          <t>111128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81471</t>
+          <t>82107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>117498</t>
+          <t>116731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87051</t>
+          <t>87801</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>148232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>193459</t>
+          <t>195866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>59832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92330</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65821</t>
+          <t>64778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106956</t>
+          <t>108018</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147215</t>
+          <t>148273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78031</t>
+          <t>77802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>66074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95200</t>
+          <t>96896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122172</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165341</t>
+          <t>167484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84292</t>
+          <t>84872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119819</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>48550</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76609</t>
+          <t>77868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143504</t>
+          <t>141302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188655</t>
+          <t>188744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>43964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71718</t>
+          <t>71682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56066</t>
+          <t>58934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83451</t>
+          <t>83269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>119902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>64910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97528</t>
+          <t>96442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54631</t>
+          <t>53595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>84353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>129457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170872</t>
+          <t>173374</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88833</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46175</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74367</t>
+          <t>75485</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>111237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>154716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74132</t>
+          <t>75011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107524</t>
+          <t>108334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108453</t>
+          <t>109301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>160948</t>
+          <t>159764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206711</t>
+          <t>207043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>275287</t>
+          <t>274410</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>337848</t>
+          <t>336913</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139725</t>
+          <t>139784</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>186839</t>
+          <t>186708</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>429336</t>
+          <t>430362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>510059</t>
+          <t>510663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>202722</t>
+          <t>201751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>254538</t>
+          <t>259851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>132506</t>
+          <t>133602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>177095</t>
+          <t>179743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>349611</t>
+          <t>348174</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>423525</t>
+          <t>421860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>277910</t>
+          <t>277351</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>339647</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>220513</t>
+          <t>220029</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>274469</t>
+          <t>274386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>510202</t>
+          <t>506435</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>597776</t>
+          <t>594762</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>269210</t>
+          <t>263615</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>331084</t>
+          <t>327968</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>170150</t>
+          <t>170678</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>219313</t>
+          <t>220339</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>453110</t>
+          <t>451812</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533570</t>
+          <t>533448</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>255223</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>313876</t>
+          <t>318256</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>251630</t>
+          <t>253052</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>308137</t>
+          <t>309143</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>525013</t>
+          <t>522439</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>604217</t>
+          <t>605933</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2023</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>53059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>27994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,47 +8257,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>19728</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13466</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>26486</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>29,04%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19728</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14278</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27337</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>25757</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46359</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31955</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58045</t>
+          <t>58863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31399</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136956</t>
+          <t>135930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73405</t>
+          <t>72963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93739</t>
+          <t>93892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122595</t>
+          <t>121518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148072</t>
+          <t>146736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40862</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356944</t>
+          <t>358067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>62987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431569</t>
+          <t>435483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>63187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>33799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95584</t>
+          <t>95534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34743</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54339</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>43701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48952</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>32346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>36069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>58368</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>20653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63114</t>
+          <t>61129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88934</t>
+          <t>87725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29930</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57512</t>
+          <t>56353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>37432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>54717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>232897</t>
+          <t>232775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95209</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>104481</t>
+          <t>108364</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300255</t>
+          <t>298808</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125799</t>
+          <t>126525</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42912</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>55393</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178398</t>
+          <t>175257</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160371</t>
+          <t>162011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81194</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109223</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>93687</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260116</t>
+          <t>262078</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73805</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>516976</t>
+          <t>521650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>42565</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130594</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>670216</t>
+          <t>701037</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107683</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85876</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66744</t>
+          <t>59919</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>183543</t>
+          <t>183385</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6706-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6706-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74924</t>
+          <t>75430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77908</t>
+          <t>78408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32084</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57397</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53127</t>
+          <t>54127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84849</t>
+          <t>82663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>42279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68966</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>75418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109788</t>
+          <t>108743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51993</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48684</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77495</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55716</t>
+          <t>56274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84936</t>
+          <t>85336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>29571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>92943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>129679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62406</t>
+          <t>62463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95294</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104078</t>
+          <t>103903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>145378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58923</t>
+          <t>58310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>89643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60813</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92099</t>
+          <t>92638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>104599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144221</t>
+          <t>143502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100684</t>
+          <t>102557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,82 +1768,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>60176</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44896</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73166</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>144015</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>121472</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>166872</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>21,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>24,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>60176</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46624</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>74678</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>144015</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>124358</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>167397</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>21,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108242</t>
+          <t>109073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150101</t>
+          <t>148966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>67822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98676</t>
+          <t>99020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187272</t>
+          <t>183944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236996</t>
+          <t>234264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>69293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42906</t>
+          <t>42290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67495</t>
+          <t>67778</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>103232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>37210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>40688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72417</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>39602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68862</t>
+          <t>66809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54957</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>76485</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>115126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54532</t>
+          <t>55679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86822</t>
+          <t>87683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41493</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81640</t>
+          <t>82068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119043</t>
+          <t>119772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98557</t>
+          <t>97658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134912</t>
+          <t>133689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68131</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97779</t>
+          <t>99294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177037</t>
+          <t>175002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>222082</t>
+          <t>221916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81362</t>
+          <t>81372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33321</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59110</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>129967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>34433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>59446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40729</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60657</t>
+          <t>60154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93426</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>82866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116887</t>
+          <t>117866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57042</t>
+          <t>55712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85175</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>148684</t>
+          <t>147634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192943</t>
+          <t>192745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>89448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125695</t>
+          <t>125649</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50379</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79126</t>
+          <t>78690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148165</t>
+          <t>147824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193102</t>
+          <t>194056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78328</t>
+          <t>78833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114502</t>
+          <t>115905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78799</t>
+          <t>76985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111305</t>
+          <t>109113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>167461</t>
+          <t>164567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213833</t>
+          <t>211925</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229336</t>
+          <t>225761</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288008</t>
+          <t>286664</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132484</t>
+          <t>129673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>180651</t>
+          <t>177216</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>371716</t>
+          <t>372392</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>443911</t>
+          <t>449590</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>138138</t>
+          <t>136972</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187647</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>135546</t>
+          <t>135161</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>244044</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>305534</t>
+          <t>308004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>250177</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>314760</t>
+          <t>311762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>170481</t>
+          <t>170042</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>224921</t>
+          <t>221584</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>437739</t>
+          <t>439168</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>521130</t>
+          <t>519210</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>268148</t>
+          <t>268667</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>333994</t>
+          <t>331125</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156088</t>
+          <t>154371</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>206083</t>
+          <t>202943</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>441441</t>
+          <t>440557</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>521942</t>
+          <t>520142</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>373341</t>
+          <t>373216</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>445488</t>
+          <t>444261</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>270177</t>
+          <t>268724</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>330129</t>
+          <t>327760</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>665191</t>
+          <t>665428</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>760057</t>
+          <t>755784</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>58808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>40605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>61066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94339</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>29445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>55177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62801</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95214</t>
+          <t>95171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64033</t>
+          <t>64605</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>30722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74618</t>
+          <t>73747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>107706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>43775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69579</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42176</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71781</t>
+          <t>73174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105555</t>
+          <t>106446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>38381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64288</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38584</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62683</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95080</t>
+          <t>95443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67196</t>
+          <t>67646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100046</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104951</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145234</t>
+          <t>145708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58553</t>
+          <t>60037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92777</t>
+          <t>93151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49234</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93605</t>
+          <t>91903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135212</t>
+          <t>132475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61066</t>
+          <t>62444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95035</t>
+          <t>95079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51558</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78598</t>
+          <t>79666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120575</t>
+          <t>121643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165789</t>
+          <t>166099</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>76902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113889</t>
+          <t>113415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40257</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65574</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167628</t>
+          <t>171501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>66205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100366</t>
+          <t>100524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66373</t>
+          <t>66022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95521</t>
+          <t>96536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141200</t>
+          <t>142031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185764</t>
+          <t>185688</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59472</t>
+          <t>59110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93332</t>
+          <t>92436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40345</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85858</t>
+          <t>83098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126818</t>
+          <t>122475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41173</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>50740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111128</t>
+          <t>111384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82107</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116731</t>
+          <t>118559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58033</t>
+          <t>58793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87801</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148232</t>
+          <t>150101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195866</t>
+          <t>194575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59832</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64778</t>
+          <t>65336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108018</t>
+          <t>106755</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148273</t>
+          <t>147507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>48786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66074</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96896</t>
+          <t>96102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>120676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167484</t>
+          <t>163416</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119891</t>
+          <t>120783</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48550</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77868</t>
+          <t>78217</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>141701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188744</t>
+          <t>187241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43964</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71682</t>
+          <t>71117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58934</t>
+          <t>57779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83269</t>
+          <t>80616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119902</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64910</t>
+          <t>65179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96442</t>
+          <t>97471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84353</t>
+          <t>84600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129457</t>
+          <t>127473</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>173374</t>
+          <t>173203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>58774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75485</t>
+          <t>73761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111237</t>
+          <t>112903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154716</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75011</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108334</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74585</t>
+          <t>75957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109301</t>
+          <t>107345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>159764</t>
+          <t>161706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207043</t>
+          <t>207747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>274410</t>
+          <t>272189</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>336913</t>
+          <t>335194</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139784</t>
+          <t>140321</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>186708</t>
+          <t>186208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>430362</t>
+          <t>428261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>510663</t>
+          <t>503910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>201751</t>
+          <t>202246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>259851</t>
+          <t>258010</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>133602</t>
+          <t>132539</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179743</t>
+          <t>179631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>348174</t>
+          <t>343519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>421860</t>
+          <t>420913</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>277351</t>
+          <t>276765</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>341040</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>220029</t>
+          <t>221415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>274386</t>
+          <t>274737</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>506435</t>
+          <t>510828</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>594762</t>
+          <t>597003</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>263615</t>
+          <t>268521</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>327968</t>
+          <t>331374</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>170678</t>
+          <t>169164</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>220339</t>
+          <t>217833</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>451812</t>
+          <t>453689</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533448</t>
+          <t>532838</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>255223</t>
+          <t>254809</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>318256</t>
+          <t>317973</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>253052</t>
+          <t>253340</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>309143</t>
+          <t>311057</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>522439</t>
+          <t>521203</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>605933</t>
+          <t>608997</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>22129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>55242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,67 +8159,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>15179</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>32706</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>19100</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>12162</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>27994</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>26165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>28018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>27455</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26876</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>48671</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>66071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>156822</t>
+          <t>175279</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>156822</t>
+          <t>175279</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>156822</t>
+          <t>175279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>47805</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>34484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123763</t>
+          <t>62613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>25567</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>73371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135930</t>
+          <t>90941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72963</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>52494</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>66790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121518</t>
+          <t>65085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>72026</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146736</t>
+          <t>98559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>262997</t>
+          <t>22401</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>358067</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>280845</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62987</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>435483</t>
+          <t>55368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63187</t>
+          <t>34030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33799</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95534</t>
+          <t>63482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>395436</t>
+          <t>170720</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>395436</t>
+          <t>170720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395436</t>
+          <t>170720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>511892</t>
+          <t>298967</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>511892</t>
+          <t>298967</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>511892</t>
+          <t>298967</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>31484</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>27950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43701</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48956</t>
+          <t>56279</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>51713</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>61560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>74991</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61129</t>
+          <t>69390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87725</t>
+          <t>98573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56353</t>
+          <t>59296</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>195899</t>
+          <t>213715</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195899</t>
+          <t>213715</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>195899</t>
+          <t>213715</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>139889</t>
+          <t>157605</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>131335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>232775</t>
+          <t>182246</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>79896</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>75624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94081</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>219785</t>
+          <t>247076</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>108364</t>
+          <t>219269</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>298808</t>
+          <t>278051</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>84230</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>65781</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126525</t>
+          <t>102180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>77353</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>128654</t>
+          <t>147501</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55393</t>
+          <t>126922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>170911</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>96363</t>
+          <t>107832</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>89034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162011</t>
+          <t>129781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>95001</t>
+          <t>103088</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82032</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111495</t>
+          <t>117797</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>191364</t>
+          <t>210920</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93687</t>
+          <t>187268</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>262078</t>
+          <t>239992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>295382</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>72398</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>521650</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>53622</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66363</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>349004</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130594</t>
+          <t>102932</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>701037</t>
+          <t>143959</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>106207</t>
+          <t>91418</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>91526</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>133645</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59919</t>
+          <t>123871</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>183385</t>
+          <t>171953</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>478785</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>478785</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>478785</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1022451</t>
+          <t>872617</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1022451</t>
+          <t>872617</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1022451</t>
+          <t>872617</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
